--- a/工作进度.xlsx
+++ b/工作进度.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\2206A\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3BC5A3-F911-4AB6-943A-3B7FE89A21E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="2730" yWindow="1820" windowWidth="22870" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +24,34 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作进度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,11 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +359,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="75.4140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/工作进度.xlsx
+++ b/工作进度.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BroHaoNB\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D07AF0-60F0-4C30-98C7-104B13BB7D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12252" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +24,34 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>吕润辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将怪物的AI逻辑合并进主分支</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,11 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +359,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A8:G8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:G8"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/工作进度.xlsx
+++ b/工作进度.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\2206A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3BC5A3-F911-4AB6-943A-3B7FE89A21E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB10DFE5-05B5-492A-9541-43AEE0388121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="1820" windowWidth="22870" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,12 +34,24 @@
     <t>工作进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>王瑞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（1）场景，技能，角色，波次刷新 类结构设计 
+（2）部分编辑器的编写
+（3）核心战斗模块编写
+（4）部分技能设计
+（5）各部分模块对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,6 +61,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -75,10 +95,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -360,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="75.4140625" customWidth="1"/>
@@ -374,6 +400,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" ht="70" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/工作进度.xlsx
+++ b/工作进度.xlsx
@@ -1,43 +1,407 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>王子龙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">功能 ： 实现了资源管理框架，AB打包，以及LRU缓存，通过资源下载的进度实时刷新进度条，在资源加载完毕之后跳转游戏主菜单   之后与其他同学对接了UI资源(面板，敌人，玩家)，
+通过将UI资源打包成AB包，然后再将需要加载的UI资源路径传入对接的加载资源接口，实现通过资源管理框架加载和销毁资源以及根据其他同学的需求实时更新框架内部逻辑
+遇到的问题 1：多开协程导致阻塞主线程  2：同时加载相同AB包文件导致报错 </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -45,24 +409,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -111,7 +767,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -146,7 +802,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -320,20 +976,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <cols>
+    <col min="2" max="2" width="128.444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="69" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/工作进度.xlsx
+++ b/工作进度.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\2206A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCB058C-BE1F-4871-B301-8A2D0FB85A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4262D58B-D0BB-4FC1-BBB2-419DAB9B4811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="1890" windowWidth="22870" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,7 +62,17 @@
   </si>
   <si>
     <t xml:space="preserve">
-</t>
+git上传冲突
+类结构设计是否合理
+伤害计算异常
+无法区分，怪物波次的问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器合成升级时，
+无法切换的问题   
+怪物刷新波次时血量异
+常的问题无法区分，怪物波次的问题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -114,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -127,6 +137,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -437,12 +450,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="70" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/工作进度.xlsx
+++ b/工作进度.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>王子龙</t>
   </si>
@@ -35,6 +35,13 @@
     <t xml:space="preserve">功能 ： 实现了资源管理框架，AB打包，以及LRU缓存，通过资源下载的进度实时刷新进度条，在资源加载完毕之后跳转游戏主菜单   之后与其他同学对接了UI资源(面板，敌人，玩家)，
 通过将UI资源打包成AB包，然后再将需要加载的UI资源路径传入对接的加载资源接口，实现通过资源管理框架加载和销毁资源以及根据其他同学的需求实时更新框架内部逻辑
 遇到的问题 1：多开协程导致阻塞主线程  2：同时加载相同AB包文件导致报错 </t>
+  </si>
+  <si>
+    <t>彭泽义</t>
+  </si>
+  <si>
+    <t>功能:ILRuntime热更新 增加了HotFix_Project工程主工程:增加了:AppDomalinLanch脚本为加载DLL文件,LoadHotFixMgr解析DLL文件和pdb文件
+遇到的问题:在加载DLL文件的时候可能会导致加载失败要选好路径</t>
   </si>
 </sst>
 </file>
@@ -47,14 +54,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,155 +510,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -982,8 +985,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="128.444444444444" customWidth="1"/>
   </cols>
@@ -996,6 +999,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" ht="27.6" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/工作进度.xlsx
+++ b/工作进度.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\2206A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New2206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCB058C-BE1F-4871-B301-8A2D0FB85A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA3267F-A18B-44B7-A620-EF09FAFDEF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="1890" windowWidth="22870" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4236" yWindow="1932" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>姓名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,6 +63,15 @@
   <si>
     <t xml:space="preserve">
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张浩然</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A星寻路 查找最优路径 已优化
+参与敌人群体移动</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -114,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -127,6 +136,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -408,14 +420,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="75.4140625" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="2" max="2" width="75.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -426,7 +438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="84" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -437,12 +449,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
